--- a/data-vh/Февраль_2026_ВХ.xlsx
+++ b/data-vh/Февраль_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$67</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,4218 +562,4567 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q67"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="46.95" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" s="13" t="n"/>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Пакет 11БПР756: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок    Дефекты ЦП:    - забоины до основного металла    - несплошность ЦП в месте контакта с подвесочной проволокой    - наплывы, препятствующие сборке</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="Q2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="46.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" s="13" t="n"/>
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Пакет 12БПР604: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок    Дефекты ЦП:    - забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="46.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Пакет 501: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок    Дефекты ЦП:    -  наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="Q4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="46.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Пакет 502: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок    Дефекты ЦП:    - забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="46.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>Пакет 503: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок.    Дефекты ЦП:    - забоины до основного металла;    - наплывы в отверстиях и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки).</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="Q6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Пакет 505: Дефекты ЦП:    - забоины до основного металла    - заплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    Мех. повреждения</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="Q7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="22.95" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>Пакет 01(А+Б+В+Г+Д): Дефекты ЦП:    -  наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="Q8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>Пакет 02А: Дефекты ЦП:    -  Наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы, препятствующие сборке    - аплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="Q9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1">
+      <c r="A10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>Пакет 03 (А+Б): Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="Q10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1">
+      <c r="A11" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Пакет 04А: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="Q11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1">
+      <c r="A12" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>Пакет 05 (А+Б+В): Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="Q12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1">
+      <c r="A13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>Пакет 06А: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="Q13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1">
+      <c r="A14" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>Пакет 07А: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="Q14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="34.95" customHeight="1">
+      <c r="A15" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>Пакет 08А: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="Q15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="34.95" customHeight="1">
+      <c r="A16" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>Пакет 09 (А+Б): Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="Q16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="34.95" customHeight="1">
+      <c r="A17" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>Пакет 10БПР31: Дефекты ЦП:    - забоины до основного металла    - несплошность ЦП в месте контакта с подвесочной проволокой    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="Q17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="34.95" customHeight="1">
+      <c r="A18" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>Пакет 13АПР600: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="Q18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="34.95" customHeight="1">
+      <c r="A19" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>Пакет 13БПР600: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="Q19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="34.95" customHeight="1">
+      <c r="A20" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>Пакет 13ВПР600: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="Q20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="22.95" customHeight="1">
+      <c r="A21" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>Пакет 14А: Дефекты ЦП:    - забоины до основного металла</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="Q21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="22.95" customHeight="1">
+      <c r="A22" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>Пакет 15А: Дефекты ЦП:    -  наплывы, препятствующие сборке</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="Q22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="34.95" customHeight="1">
+      <c r="A23" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="M23" s="13" t="n"/>
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>Пакет 500: Дефекты ЦП:    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="Q23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="22.95" customHeight="1">
+      <c r="A24" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>Пакет 504: Дефекты ЦП:    - забоины до основного металла</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="Q24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="22.95" customHeight="1">
+      <c r="A25" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>Пакет 506: Дефекты ЦП:    - забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="Q25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="22.95" customHeight="1">
+      <c r="A26" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>Пакет 507: Дефекты ЦП:    - забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="Q26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="46.95" customHeight="1">
+      <c r="A27" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>В00-0000014</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>03.02.2026</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000057 от 03.02.2026 9:57:49</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Склад ПФ</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Ствол опоры ФГН-10,0-02 (ОО 270.01.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="10" t="n">
         <v>1661.88</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>1. Брызги металла. 2. Сварной шов №4 выполнен с прерываниями по незамкнутому контуру. 3. Натёки. 4. Несплавление. 5. Подрезы. 6. Асимметрия сварного шва №4. 7. Межваликовый подрез. 8. По КД расстояние внутри лючка 98+0,5-1мм, фактически до 99.44мм.</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами сотрудников</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" ht="46.95" customHeight="1">
+      <c r="A28" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>В00-0000015</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>04.02.2026</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х22,2/30х2 1 А 996х1000 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="12" t="n">
         <v>3250</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>Прожог.     Брызги металла диаметром более 1,5 мм.     Соединение полос несущих и обрамления:     - несплавление (отсутствие соединения между основным и наплавленным металлом);     - неправильная форма сварного шва (отклонение от требуемой формы и геометрии).</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранить силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" ht="22.95" customHeight="1">
+      <c r="A29" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>В00-0000016</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>05.02.2026</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-000624 от 04.02.2026 23:56:11</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>ЕВРАЗ Маркет (ЕВРАЗ Металл Инпром) (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>_уу_Труба 80*40*2,0 ГОСТ 8645-68/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>2.1.1.2.1.3 Труба прямоугольная ГОСТ 8645-68</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="9" t="n">
         <v>21.36</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="9" t="n">
         <v>21.36</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>Вогнутость на стороне 80мм до 5,2мм, по ГОСТ 8639 допускается не более 1мм.</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>Взять в работу с доработкой</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" ht="58.95" customHeight="1">
+      <c r="A30" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>В00-0000017</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>06.02.2026</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="14" t="n">
         <v>6178.3</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>ОР 021.02.00.000СБ:    Соед. деталей 2 и 1 Т1 катет 8 - фактически катет 6-8 мм.     Дефекты сварных швов: подрезы, брызги металла, наплывы, поры, плохое повторное возбуждение дуги.     ОР 001.01.001:    Шероховатость поверхностей (отверстия, торцы) термической резки более Rz 80, в наличие дефекты термической резки: неравномерная глубина линий бороздок, выхватывание.</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчиков</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" ht="22.95" customHeight="1">
+      <c r="A31" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>В00-0000018</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>06.02.2026</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-000193 от 21.01.2026 12:06:41</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>СЕВЕРСТАЛЬ ДИСТРИБУЦИЯ АО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>_уу_Г/к штрипс 2,9*468 (0+2)/S235JR</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>Штрипсы</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="12" t="n">
         <v>4497</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="12" t="n">
         <v>4497</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="7" t="inlineStr">
         <is>
           <t>Взять в работу с доработкой</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" ht="22.95" customHeight="1">
+      <c r="A32" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>В00-0000019</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>09.02.2026</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000076 от 09.02.2026 10:56:50</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Склад для переработчиков</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>ГПСкомпл(60) Световозвращатель КД5-КБII-RI / (ЭС-2) СТО 07525912-030-2016</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>1.1.8.1 Световозвращатель ЭС-2 (КД5-КБII-RI)</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="12" t="n">
         <v>3600</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="12" t="n">
         <v>1512</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>Несоответствие геометрических размеров</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Малозначительное</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>1. Размер по КД 4+-1 мм, фактически 2 мм. 2. Размер по КД 5+-1 мм, фактически 3 мм.</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" s="7" t="inlineStr">
         <is>
           <t>КР №9 от 10.02.2026</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" ht="46.95" customHeight="1">
+      <c r="A33" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>В00-0000020</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>09.02.2026</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000067 от 06.02.2026 12:00:00</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП10-01 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="10" t="n">
         <v>1763.98</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, несплавления, плохое повторное возбуждение дуги. ОР 001.01.001: Шероховатость поверхностей (отверстия, торцы) термической резки более Rz 80, в наличие дефекты термической резки: неравномерная глубина линий бороздок, выхватывание.</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" s="7" t="inlineStr">
         <is>
           <t>Несоттветствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" ht="46.95" customHeight="1">
+      <c r="A34" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>В00-0000020</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>09.02.2026</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000067 от 06.02.2026 12:00:00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="10" t="n">
         <v>4108.02</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, несплавления, плохое повторное возбуждение дуги. ОР 001.01.001: Шероховатость поверхностей (отверстия, торцы) термической резки более Rz 80, в наличие дефекты термической резки: неравномерная глубина линий бороздок, выхватывание.</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" s="7" t="inlineStr">
         <is>
           <t>Несоттветствия устранены переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" ht="22.95" customHeight="1">
+      <c r="A35" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>В00-0000021</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>09.02.2026</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-000655 от 06.02.2026 14:57:41</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>Строд Сервис (Самара) (ЭДО Такском ЗП 06.02.25)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>_уу_Знак дорожный 4.2.1 (4.2.2) III типоразмер тип пленки Б со светодиодной поворотной стрелкой на к</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>ОМФП</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="9" t="n">
         <v>15.24</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="7" t="inlineStr">
         <is>
           <t>Несоответствие геометрических размеров</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>По КД диаметр отверстий 12+2мм, фактически 9,9мм. По КД межосевое расстояние отверстий 650+-2мм, фактически 660мм.</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>Доработано силами сотрудников ОЭУ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" ht="46.95" customHeight="1">
+      <c r="A36" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>В00-0000023</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>10.02.2026</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000084 от 10.02.2026 9:24:03</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Ствол опоры ФГН-10,0-02 (ОО 270.01.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="L36" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="10" t="n">
         <v>2215.84</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P36" s="7" t="inlineStr">
         <is>
           <t>1. Брызги металла. 2. Сварной шов №1 и №4 выполнен с прерываниями по незамкнутому контуру. 3. Поры. 4. Свищ. 5. Натёки. 6. Несплавления. 7. Подрезы. 8. Неравномерная ширина шва. 9. Ширина лючка по КД 98+0,5-1мм, фактически от 96,5мм.</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" s="7" t="inlineStr">
         <is>
           <t>Устранено переработчиком</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" ht="22.95" customHeight="1">
+      <c r="A37" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>В00-0000024</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>10.02.2026</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001865 от 14.04.2025 16:02:13</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>СЕВЕРСТАЛЬ ДИСТРИБУЦИЯ АО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>_уу_Г/к штрипс 2,9*125/Ст3сп</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Штрипсы</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="12" t="n">
         <v>1245</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="12" t="n">
         <v>1245</v>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="7" t="inlineStr">
         <is>
           <t>Отклонение формообразования и линейных размеров</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>Серповидность до 100 мм, по спецификации 40/5-3336 не более 5мм/5м.</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="Q37" s="7" t="n"/>
+    </row>
+    <row r="38" ht="22.95" customHeight="1">
+      <c r="A38" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>В00-0000024</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>10.02.2026</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001865 от 14.04.2025 16:02:13</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>СЕВЕРСТАЛЬ ДИСТРИБУЦИЯ АО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>_уу_Г/к штрипс 2,9*125/Ст3сп</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>Штрипсы</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="12" t="n">
         <v>1595</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="12" t="n">
         <v>1595</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>Отклонение формообразования и линейных размеров</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P38" s="7" t="inlineStr">
         <is>
           <t>Серповидность до 75 мм, по спецификации 40/5-3336 не более 5мм/5м.</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+      <c r="Q38" s="7" t="n"/>
+    </row>
+    <row r="39" ht="22.95" customHeight="1">
+      <c r="A39" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>В00-0000024</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>10.02.2026</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001865 от 14.04.2025 16:02:13</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>СЕВЕРСТАЛЬ ДИСТРИБУЦИЯ АО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>_уу_Г/к штрипс 2,9*125/Ст3сп</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>Штрипсы</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="12" t="n">
         <v>1574</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="12" t="n">
         <v>1574</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>Отклонение формообразования и линейных размеров</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>Серповидность до 92 мм, по спецификации 40/5-3336 не более 5мм/5м.</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="Q39" s="7" t="n"/>
+    </row>
+    <row r="40" ht="22.95" customHeight="1">
+      <c r="A40" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>В00-0000026</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000091 от 10.02.2026 15:04:50</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х22,2/30х2 1 А 996х1000 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="8" t="n">
         <v>812.5</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>Соединение крайних несущих полос обрамления выполнено на прихватках по КД сварной шов №1 Т1 катет 2. Прожоги.</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="Q40" s="7" t="n"/>
+    </row>
+    <row r="41" ht="34.95" customHeight="1">
+      <c r="A41" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>В00-0000026</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000091 от 10.02.2026 15:04:50</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х22,2/30х2 1 А 996х1000 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="L41" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" s="9" t="n">
         <v>406.25</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P41" s="7" t="inlineStr">
         <is>
           <t>Соединение крайних несущих полос обрамления выполнено на прихватках по КД сварной шов №1 Т1 катет 2. Шов выполненый методом лазерной сварки неполной длины.</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="Q41" s="7" t="n"/>
+    </row>
+    <row r="42" ht="34.95" customHeight="1">
+      <c r="A42" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>В00-0000026</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000091 от 10.02.2026 15:04:50</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х22,2/30х2 1 А 996х1000 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="L42" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42" s="14" t="n">
         <v>2437.5</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P42" s="7" t="inlineStr">
         <is>
           <t>Соединение крайних несущих полос обрамления выполнено на прихватках по КД сварной шов №1 Т1 катет 2; единичные прихваточные валики расположены на одной из свариваемых полос (ассиметприя сварных швов).</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+      <c r="Q42" s="7" t="n"/>
+    </row>
+    <row r="43" ht="22.95" customHeight="1">
+      <c r="A43" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>В00-0000026</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000091 от 10.02.2026 15:04:50</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х22,2/30х2 1 А 996х1000 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="L43" s="3" t="n">
         <v>325</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" s="10" t="n">
         <v>5281.25</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P43" s="7" t="inlineStr">
         <is>
           <t>Соединение крайних несущих полос обрамления выполнено на прихватках по КД сварной шов №1 Т1 катет 2</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" s="7" t="inlineStr">
         <is>
           <t>Доработано переработчиком 19.02.2026 в корпусе 8</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" ht="22.95" customHeight="1">
+      <c r="A44" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>В00-0000027</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000087 от 10.02.2026 15:04:49</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР9 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="L44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44" s="10" t="n">
         <v>1757.76</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P44" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, наплывы, отс. замыкание тавровых швов («закольцовки»), подрезы.</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
+      <c r="Q44" s="7" t="n"/>
+    </row>
+    <row r="45" ht="22.95" customHeight="1">
+      <c r="A45" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>В00-0000027</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000087 от 10.02.2026 15:04:49</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР14 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="L45" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45" s="9" t="n">
         <v>659.47</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P45" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, наплывы, отс. замыкание тавровых швов («закольцовки»), подрезы.</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
+      <c r="Q45" s="7" t="n"/>
+    </row>
+    <row r="46" ht="22.95" customHeight="1">
+      <c r="A46" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>В00-0000027</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000087 от 10.02.2026 15:04:49</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="L46" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M46" s="10" t="n">
         <v>3089.15</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P46" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, наплывы, отс. замыкание тавровых швов («закольцовки»), подрезы.</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
+      <c r="Q46" s="7" t="n"/>
+    </row>
+    <row r="47" ht="22.95" customHeight="1">
+      <c r="A47" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>В00-0000027</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000087 от 10.02.2026 15:04:49</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР6 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="L47" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47" s="10" t="n">
         <v>1618.42</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, наплывы, отс. замыкание тавровых швов («закольцовки»), подрезы.</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+      <c r="Q47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="22.95" customHeight="1">
+      <c r="A48" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>В00-0000028</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000088 от 11.02.2026 5:26:24</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="L48" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M48" s="10" t="n">
         <v>5477.36</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N48" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P48" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, отс. замыкание тавровых швов («закольцовки»), подрезы.</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="Q48" s="7" t="n"/>
+    </row>
+    <row r="49" ht="22.95" customHeight="1">
+      <c r="A49" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>В00-0000029</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>11.02.2026</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000089 от 11.02.2026 9:09:33</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="L49" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49" s="10" t="n">
         <v>2054.01</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P49" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, отс. замыкание тавровых швов («закольцовки»), подрезы.</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
+      <c r="Q49" s="7" t="n"/>
+    </row>
+    <row r="50" ht="70.95" customHeight="1">
+      <c r="A50" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>В00-0000030</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>13.02.2026</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>ВПК-КОНЦЕПТ ООО (6312129392) (ЭДО Такском ЗП с 01.04.25)</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(80 мкм / 80 мкм (RAL 9003)) Кронштейн 36.К1-2,0/1,5-2,0-Чайка-цп</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="L50" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M50" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N50" s="7" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P50" s="7" t="inlineStr">
         <is>
           <t>Покрытие глянцевое, VII класс, Ral 9003. Шагрень, волнистость, включения (обусловлены поверхностью цинкового покрытия), булавочные проколы, включения (не обусловленные поверхностью цинкового покрытия), наносные загрязнения ЛКМ другого цвета.     Толщина ЛКП от 120 мкм до 321 мкм.    Отсутствие ЛКП на отдельных участках до 5 мм в диаметре (места контакта с подвесочной проволокой).</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" ht="22.95" customHeight="1">
+      <c r="A51" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>В00-0000031</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="16" t="inlineStr">
         <is>
           <t>13.02.2026</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000103 от 13.02.2026 9:36:25</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="L51" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M51" s="10" t="n">
         <v>3089.15</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям РД/договорным документа</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P51" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, наплывы, отс. замыкание тавровых швов («закольцовки»), подрезы.</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+      <c r="Q51" s="7" t="n"/>
+    </row>
+    <row r="52" ht="22.95" customHeight="1">
+      <c r="A52" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>В00-0000032</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>17.02.2026</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L52" t="n">
+      <c r="L52" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M52" s="10" t="n">
         <v>4792.69</v>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P52" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, наплывы</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
+      <c r="Q52" s="7" t="n"/>
+    </row>
+    <row r="53" ht="22.95" customHeight="1">
+      <c r="A53" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>В00-0000032</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>17.02.2026</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП9 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L53" t="n">
+      <c r="L53" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53" s="9" t="n">
         <v>656.26</v>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P53" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, наплывы</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
+      <c r="Q53" s="7" t="n"/>
+    </row>
+    <row r="54" ht="10.95" customHeight="1">
+      <c r="A54" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>В00-0000033</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>17.02.2026</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР6 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="L54" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M54" s="9" t="n">
         <v>809.21</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N54" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P54" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
+      <c r="Q54" s="7" t="n"/>
+    </row>
+    <row r="55" ht="22.95" customHeight="1">
+      <c r="A55" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>В00-0000033</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="16" t="inlineStr">
         <is>
           <t>17.02.2026</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="L55" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M55" s="10" t="n">
         <v>6796.13</v>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N55" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P55" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, наплывы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
+      <c r="Q55" s="7" t="n"/>
+    </row>
+    <row r="56" ht="46.95" customHeight="1">
+      <c r="A56" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>В00-0000034</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>19.02.2026</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>ВПК-КОНЦЕПТ ООО (6312129392) (ЭДО Такском ЗП с 01.04.25)</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="I56" s="7" t="n"/>
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(80 мкм / 80 мкм (RAL 9003)) Кронштейн 36.К1-2,0/1,5-2,0-Чайка-цп</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="L56" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M56" s="12" t="n">
         <v>1564</v>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P56" s="7" t="inlineStr">
         <is>
           <t>Покрытие глянцевое, VII класс. Шагрень, включения (обусловлены поверхностью цинкового покрытия), булавочные проколы, включения (не обусловленные поверхностью цинкового покрытия). Толщина ЛКП от 112 мкм до 361 мкм. Отсутствие ЛКП на отдельных участках до 1 мм (технологические отверстия).</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" ht="22.95" customHeight="1">
+      <c r="A57" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>В00-0000035</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР18 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L57" t="n">
+      <c r="L57" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M57" s="10" t="n">
         <v>2342.76</v>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N57" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P57" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, подрезы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
+      <c r="Q57" s="7" t="n"/>
+    </row>
+    <row r="58" ht="22.95" customHeight="1">
+      <c r="A58" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>В00-0000035</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="22" t="n"/>
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L58" t="n">
+      <c r="L58" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M58" s="10" t="n">
         <v>5560.47</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P58" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, подрезы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
+      <c r="Q58" s="7" t="n"/>
+    </row>
+    <row r="59" ht="22.95" customHeight="1">
+      <c r="A59" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>В00-0000035</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="22" t="n"/>
+      <c r="E59" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР7 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L59" t="n">
+      <c r="L59" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M59" s="10" t="n">
         <v>1174.46</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N59" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P59" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, подрезы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
+      <c r="Q59" s="7" t="n"/>
+    </row>
+    <row r="60" ht="22.95" customHeight="1">
+      <c r="A60" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t>В00-0000035</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР6 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L60" t="n">
+      <c r="L60" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M60" s="10" t="n">
         <v>1618.42</v>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N60" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P60" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, подрезы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+      <c r="Q60" s="7" t="n"/>
+    </row>
+    <row r="61" ht="34.95" customHeight="1">
+      <c r="A61" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>В00-0000036</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>ВПК-КОНЦЕПТ ООО (6312129392) (ЭДО Такском ЗП с 01.04.25)</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="I61" s="7" t="n"/>
+      <c r="J61" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(80 мкм / 80 мкм (RAL 9003)) Кронштейн 36.К1-2,0/1,5-2,0-Чайка-цп</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L61" t="n">
+      <c r="L61" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M61" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N61" s="7" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P61" s="7" t="inlineStr">
         <is>
           <t>Покрытие глянцевое, VII класс. Шагрень, включения (обусловлены поверхностью цинкового покрытия), булавочные проколы, включения (не обусловленные поверхностью цинкового покрытия). Толщина ЛКП от 124 мкм до 493 мкм.</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q61" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" ht="10.95" customHeight="1">
+      <c r="A62" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>В00-0000037</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="22" t="n"/>
+      <c r="E62" s="16" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР18 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="L62" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62" s="10" t="n">
         <v>1171.38</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N62" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P62" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, отс. замыкание таврового шва («закольцовки»).</t>
         </is>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
+      <c r="Q62" s="7" t="n"/>
+    </row>
+    <row r="63" ht="10.95" customHeight="1">
+      <c r="A63" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>В00-0000037</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="16" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР14 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L63" t="n">
+      <c r="L63" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63" s="10" t="n">
         <v>1318.94</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N63" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P63" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
+      <c r="Q63" s="7" t="n"/>
+    </row>
+    <row r="64" ht="10.95" customHeight="1">
+      <c r="A64" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>В00-0000037</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="22" t="n"/>
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K64" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L64" t="n">
+      <c r="L64" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M64" s="10" t="n">
         <v>1853.49</v>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P64" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
+      <c r="Q64" s="7" t="n"/>
+    </row>
+    <row r="65" ht="10.95" customHeight="1">
+      <c r="A65" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>В00-0000037</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="16" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР6 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K65" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L65" t="n">
+      <c r="L65" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M65" s="9" t="n">
         <v>809.21</v>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N65" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P65" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
+      <c r="Q65" s="7" t="n"/>
+    </row>
+    <row r="66" ht="22.95" customHeight="1">
+      <c r="A66" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>В00-0000038</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="16" t="inlineStr">
         <is>
           <t>25.02.2026</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-000871 от 18.02.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr">
         <is>
           <t>ИО ТЕХНОЛОДЖИ ООО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>Корпус №09</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="7" t="inlineStr">
         <is>
           <t>_уу_Блок световой ИСС 2-200 24В/8Вт IP68</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" s="7" t="inlineStr">
         <is>
           <t>ОМФП</t>
         </is>
       </c>
-      <c r="L66" t="n">
+      <c r="L66" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="M66" s="13" t="n"/>
+      <c r="N66" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P66" s="7" t="inlineStr">
         <is>
           <t>Кабельный ввод не закреплен на задней панели</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q66" s="7" t="inlineStr">
         <is>
           <t>Замена поставщиком</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" ht="22.95" customHeight="1">
+      <c r="A67" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>В00-0000039</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="22" t="n"/>
+      <c r="E67" s="16" t="inlineStr">
         <is>
           <t>26.02.2026</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х22,2/30х2 1 А 996х1000 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L67" t="n">
+      <c r="L67" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="M67" t="n">
+      <c r="M67" s="10" t="n">
         <v>3656.25</v>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P67" s="7" t="inlineStr">
         <is>
           <t>1. Брызги металла диаметром более 1,5 мм. 2. Остатки сварочной проволоки. 3. Натёки.</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q67" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранить силами переработчика</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q67">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="67">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>